--- a/PsychoPy/Introtext.xlsx
+++ b/PsychoPy/Introtext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas/Documents/Experiments/Mood4/github_Mood4/PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E062C0-34AD-B448-9B8D-164491908910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7517028-1AC8-A94C-B5D4-23D2B8EF6715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2980" yWindow="600" windowWidth="41600" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
   </bookViews>
@@ -32,12 +32,14 @@
     <t>In the next few steps, we will guide you through the task and how it works, you will then do a minimum of 10 practice trials, and finally, you will start the task.</t>
   </si>
   <si>
-    <t>You will begin the task with $5. The outcome of the choices you make from then on will count for ADDITIONAL money.
-Please select your option by pressing the LEFT or RIGHT arrow keys, or either, if you are shown only one option. Once you’ve made your choice, the outcome will be applied to your total. 
-On the next screen, you will do a few introductory trials.</t>
+    <t>On each trial, you will have the opportunity to earn money by choosing between two options: a guaranteed reward, or a gamble.
+The gamble's probability of winning is indicated by a percentage. Each gamble has two possible outcomes: you either win the indicated reward, or you lose and earn $0.
+On some trials, you will only be shown a single option, which you must select to proceed.</t>
   </si>
   <si>
-    <t>On each trial, you will have the opportunity to earn money. You will be presented with two options: one option will be a certain reward, the other, a gamble. The gamble probability will be indicated by the percentage number. The gamble has two possible outcomes: either you win and gain the indicated reward, or you lose and earn $0. On some trials, you will only be presented with one option, you will have to selected it.</t>
+    <t>You will begin the task with $5. The outcome of the choices you make from then on will count for ADDITIONAL money.
+Please select your option by pressing the LEFT or RIGHT arrow key. Once you’ve made your choice, the outcome will be applied to your total.
+On the next screen, you will do a few introductory trials.</t>
   </si>
 </sst>
 </file>
@@ -922,24 +924,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="256" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="192" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="131" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/PsychoPy/Introtext.xlsx
+++ b/PsychoPy/Introtext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas/Documents/Experiments/Mood4/github_Mood4/PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7517028-1AC8-A94C-B5D4-23D2B8EF6715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292D8C56-0C01-7E40-8B92-81408F866532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2980" yWindow="600" windowWidth="41600" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
   </bookViews>
@@ -32,14 +32,15 @@
     <t>In the next few steps, we will guide you through the task and how it works, you will then do a minimum of 10 practice trials, and finally, you will start the task.</t>
   </si>
   <si>
-    <t>On each trial, you will have the opportunity to earn money by choosing between two options: a guaranteed reward, or a gamble.
-The gamble's probability of winning is indicated by a percentage. Each gamble has two possible outcomes: you either win the indicated reward, or you lose and earn $0.
-On some trials, you will only be shown a single option, which you must select to proceed.</t>
-  </si>
-  <si>
     <t>You will begin the task with $5. The outcome of the choices you make from then on will count for ADDITIONAL money.
 Please select your option by pressing the LEFT or RIGHT arrow key. Once you’ve made your choice, the outcome will be applied to your total.
 On the next screen, you will do a few introductory trials.</t>
+  </si>
+  <si>
+    <t>On each trial, you will have the opportunity to earn money by choosing between two options: a guaranteed reward, or a gamble.
+The gamble's probability of winning is indicated by a percentage. Each gamble has two possible outcomes: you either win the indicated reward, or you lose and earn $0.
+On some trials, you will only be shown a single option, which you must select to proceed.
+While the reward amounts are small, you will complete about 200 trials, and these amounts will quickly add up.</t>
   </si>
 </sst>
 </file>
@@ -936,12 +937,12 @@
     </row>
     <row r="4" spans="1:1" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="131" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/PsychoPy/Introtext.xlsx
+++ b/PsychoPy/Introtext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas/Documents/Experiments/Mood4/github_Mood4/PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292D8C56-0C01-7E40-8B92-81408F866532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241B897D-5EEF-E04B-A48D-38EAE2F8AA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2980" yWindow="600" windowWidth="41600" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
   </bookViews>
@@ -39,8 +39,7 @@
   <si>
     <t>On each trial, you will have the opportunity to earn money by choosing between two options: a guaranteed reward, or a gamble.
 The gamble's probability of winning is indicated by a percentage. Each gamble has two possible outcomes: you either win the indicated reward, or you lose and earn $0.
-On some trials, you will only be shown a single option, which you must select to proceed.
-While the reward amounts are small, you will complete about 200 trials, and these amounts will quickly add up.</t>
+On some trials, you will only be shown a single option, which you must select to proceed.</t>
   </si>
 </sst>
 </file>

--- a/PsychoPy/Introtext.xlsx
+++ b/PsychoPy/Introtext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas/Documents/Experiments/Mood4/github_Mood4/PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241B897D-5EEF-E04B-A48D-38EAE2F8AA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8277BD58-EBBF-614D-A8BA-B9EAEEF943AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2980" yWindow="600" windowWidth="41600" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
   </bookViews>
@@ -32,14 +32,14 @@
     <t>In the next few steps, we will guide you through the task and how it works, you will then do a minimum of 10 practice trials, and finally, you will start the task.</t>
   </si>
   <si>
-    <t>You will begin the task with $5. The outcome of the choices you make from then on will count for ADDITIONAL money.
-Please select your option by pressing the LEFT or RIGHT arrow key. Once you’ve made your choice, the outcome will be applied to your total.
-On the next screen, you will do a few introductory trials.</t>
-  </si>
-  <si>
     <t>On each trial, you will have the opportunity to earn money by choosing between two options: a guaranteed reward, or a gamble.
 The gamble's probability of winning is indicated by a percentage. Each gamble has two possible outcomes: you either win the indicated reward, or you lose and earn $0.
 On some trials, you will only be shown a single option, which you must select to proceed.</t>
+  </si>
+  <si>
+    <t>You will begin the task with $5.50. The outcome of the choices you make from then on will count for ADDITIONAL money.
+Please select your option by pressing the LEFT or RIGHT arrow key. Once you’ve made your choice, the outcome will be applied to your total.
+On the next screen, you will do a few introductory trials.</t>
   </si>
 </sst>
 </file>
@@ -936,12 +936,12 @@
     </row>
     <row r="4" spans="1:1" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="131" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/PsychoPy/Introtext.xlsx
+++ b/PsychoPy/Introtext.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas/Documents/Experiments/Mood4/github_Mood4/PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8277BD58-EBBF-614D-A8BA-B9EAEEF943AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5A2E43-BF74-EA47-83C4-2B3339C6CE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2980" yWindow="600" windowWidth="41600" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
   </bookViews>
@@ -32,14 +32,14 @@
     <t>In the next few steps, we will guide you through the task and how it works, you will then do a minimum of 10 practice trials, and finally, you will start the task.</t>
   </si>
   <si>
+    <t>You will begin the task with $5.50. The outcome of the choices you make from then on will count for ADDITIONAL money.
+Please select your option by pressing the LEFT or RIGHT arrow key. Once you’ve made your choice, the outcome will be applied to your total.
+On the next screen, you will do a few introductory trials.</t>
+  </si>
+  <si>
     <t>On each trial, you will have the opportunity to earn money by choosing between two options: a guaranteed reward, or a gamble.
 The gamble's probability of winning is indicated by a percentage. Each gamble has two possible outcomes: you either win the indicated reward, or you lose and earn $0.
 On some trials, you will only be shown a single option, which you must select to proceed.</t>
-  </si>
-  <si>
-    <t>You will begin the task with $5.50. The outcome of the choices you make from then on will count for ADDITIONAL money.
-Please select your option by pressing the LEFT or RIGHT arrow key. Once you’ve made your choice, the outcome will be applied to your total.
-On the next screen, you will do a few introductory trials.</t>
   </si>
 </sst>
 </file>
@@ -936,12 +936,12 @@
     </row>
     <row r="4" spans="1:1" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="131" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
